--- a/data_extactor/batch/1000_1017.xlsx
+++ b/data_extactor/batch/1000_1017.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AD0794-DA60-43C5-BE33-EC2947306276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,448 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="145">
+  <si>
+    <t>55-1013.00</t>
+  </si>
+  <si>
+    <t>Armored Assault Vehicle Officers</t>
+  </si>
+  <si>
+    <t>Armor Officer | Armored Assault Vehicle Platoon Leader | Cavalry Officer | Tank Commander | Tank Platoon Leader | Armor Platoon Commander | Amphibious Assault Vehicle Officer | Armored Cavalry Officer | Tank Company Commander | Armored Unit Commander</t>
+  </si>
+  <si>
+    <t>Geographic information system GIS software | Digital mapping software | Terrain surface mapping software | Route mapping software | Navigation software | Simulation and modeling software | Radar software | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Email software | Satellite image databases | Logistics management information LMI database software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Monitoring | Reading Comprehension | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Geography | Transportation | Mechanical | Administration and Management | Telecommunications | English Language | Engineering and Technology | Personnel and Human Resources | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Spatial Orientation | Reaction Time | Depth Perception | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Cramped Work Space, Awkward Positions | Exposed to Whole Body Vibration</t>
+  </si>
+  <si>
+    <t>Police and Sheriff's Patrol Officers | First-Line Supervisors of Police and Detectives | Detectives and Criminal Investigators | Firefighters | First-Line Supervisors of Firefighting and Prevention Workers | Security Guards | Correctional Officers and Jailers | Emergency Management Directors | Transportation Security Screeners | Emergency Medical Technicians | General and Operations Managers | Logisticians | Transportation, Storage, and Distribution Managers | Chief Executives | Training and Development Specialists | Occupational Health and Safety Specialists | Compliance Officers | Surveying and Mapping Technicians | Explosives Workers, Ordnance Handling Experts, and Blasters | Hazardous Materials Removal Workers</t>
+  </si>
+  <si>
+    <t>Direct the operation of tanks, light armor, and amphibious assault vehicle units during combat situations on land or in aquatic environments. Duties include directing crew members in the operation of targeting and firing systems; coordinating the operation of advanced onboard communications and navigation equipment; directing the transport of personnel and equipment during combat; formulating and implementing battle plans, including the tactical employment of armored vehicle units; and coordinating with infantry, artillery, and air support units.</t>
+  </si>
+  <si>
+    <t>Direct the operation of tanks, light armor, and amphibious assault vehicle units during combat operations. | Direct crew members in the operation of targeting and firing systems. | Coordinate the operation of advanced onboard communications and navigation equipment. | Plan and lead tactical movement of armored units over varied terrain and in aquatic environments. | Evaluate terrain, obstacles, and enemy dispositions to select routes and firing positions. | Coordinate armored operations with infantry, artillery, aviation, and engineer units. | Direct the maintenance, recovery, and combat readiness of assigned vehicles and weapons systems. | Establish and enforce vehicle safety, ammunition handling, and crew discipline standards. | Train and evaluate crew members in gunnery, driving, communications, and maintenance tasks. | Develop operation orders, fire plans, and contingency plans for assigned missions. | Monitor fuel, ammunition, and supply status and coordinate resupply operations. | Direct the camouflage, concealment, and defensive preparation of unit positions. | Prepare after-action reports documenting unit performance and lessons learned. | Supervise the accountability and security of sensitive equipment and classified materials. | Advise senior commanders on the tactical employment of armored forces.</t>
+  </si>
+  <si>
+    <t>55-1014.00</t>
+  </si>
+  <si>
+    <t>Artillery and Missile Officers</t>
+  </si>
+  <si>
+    <t>Air Defense Artillery Officer | Artillery Officer | Field Artillery Officer | Fire Direction Officer | Fire Support Officer | Missile Battery Commander | Missile Launch Officer | Artillery Battery Commander | Naval Gunnery Officer | Air and Missile Defense Officer</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Monitoring | Reading Comprehension | Active Learning | Writing | Learning Strategies | Mathematics</t>
+  </si>
+  <si>
+    <t>Mathematics | Public Safety and Security | Physics | Geography | Engineering and Technology | Administration and Management | Telecommunications | English Language | Computers and Electronics | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Mathematical Reasoning | Number Facility | Spatial Orientation | Reaction Time</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Under Cover</t>
+  </si>
+  <si>
+    <t>Manage personnel and weapons operations to destroy enemy positions, aircraft, and vessels. Duties include planning, targeting, and coordinating the tactical deployment of field artillery and air defense artillery missile systems units; directing the establishment and operation of fire control communications systems; targeting and launching intercontinental ballistic missiles; directing the storage and handling of nuclear munitions and components; overseeing security of weapons storage and launch facilities; and managing maintenance of weapons systems.</t>
+  </si>
+  <si>
+    <t>Manage personnel and weapons operations to destroy enemy positions, aircraft, and vessels. | Plan, target, and coordinate the tactical deployment of field artillery and air defense artillery missile systems units. | Direct the establishment and operation of fire control communications networks. | Compute and verify firing data, including range, azimuth, elevation, and ammunition selection. | Coordinate indirect fire support with maneuver, aviation, and joint force commanders. | Direct the emplacement, survey, and displacement of firing batteries and launch positions. | Enforce ammunition handling, storage, and safety procedures for conventional and guided munitions. | Supervise the maintenance and readiness of guns, launchers, radars, and fire control systems. | Analyze target acquisition data from radar, forward observers, and unmanned systems. | Train and evaluate crews in gunnery procedures, fire direction, and emergency actions. | Develop fire support plans, target lists, and rules of engagement for assigned operations. | Monitor airspace coordination measures to prevent fratricide and civilian casualties. | Prepare readiness reports, ammunition expenditure records, and after-action reviews. | Coordinate logistics, resupply, and transportation for artillery and missile units. | Advise senior commanders on the capabilities and employment of fire support assets.</t>
+  </si>
+  <si>
+    <t>55-1015.00</t>
+  </si>
+  <si>
+    <t>Command and Control Center Officers</t>
+  </si>
+  <si>
+    <t>Battle Watch Captain | Combat Information Center Officer | Command Center Officer | Operations Officer | Tactical Action Officer | Air Battle Manager | Combat Operations Officer | Command and Control Officer | Watch Officer | Joint Operations Center Officer</t>
+  </si>
+  <si>
+    <t>Radar software | Flight simulation software | Navigation software | Geographic information system GIS software | Digital mapping software | Satellite database software | Simulation and modeling software | Electronic aircraft information databases | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Email software | Terrain surface mapping software | Satellite image databases</t>
+  </si>
+  <si>
+    <t>Telecommunications | Computers and Electronics | Public Safety and Security | Administration and Management | Geography | English Language | Transportation | Engineering and Technology | Communications and Media | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Auditory Attention | Perceptual Speed | Flexibility of Closure | Speed of Closure</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Indoors, Environmentally Controlled | Spend Time Sitting | Importance of Repeating Same Tasks | Degree of Automation | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Airline Pilots, Copilots, and Flight Engineers | Commercial Pilots | Air Traffic Controllers | Airfield Operations Specialists | Aircraft Mechanics and Service Technicians | Avionics Technicians | Aerospace Engineers | Aerospace Engineering and Operations Technologists and Technicians | Emergency Management Directors | Transportation, Storage, and Distribution Managers | Logisticians | General and Operations Managers | Chief Executives | First-Line Supervisors of Police and Detectives | Detectives and Criminal Investigators | Police and Sheriff's Patrol Officers | Security Guards | Transportation Security Screeners | Training and Development Specialists | Occupational Health and Safety Specialists</t>
+  </si>
+  <si>
+    <t>Manage the operation of communications, detection, and weapons systems essential for controlling air, ground, and naval operations. Duties include managing critical communication links between air, naval, and ground forces; formulating and implementing emergency plans for natural and wartime disasters; coordinating emergency response teams and agencies; evaluating command center information and need for high-level military and government reporting; managing the operation of surveillance and detection systems; providing technical information and advice on capabilities and operational readiness; and directing operation of weapons targeting, firing, and launch computer systems.</t>
+  </si>
+  <si>
+    <t>Manage the operation of communications, detection, and weapons systems essential for controlling air, ground, and naval operations. | Manage critical communication links between air, naval, and ground forces. | Formulate and implement emergency plans for natural and wartime disasters. | Direct the collection, evaluation, and dissemination of tactical information to commanders. | Monitor radar, sensor, and intelligence feeds to maintain a common operational picture. | Coordinate airspace control measures and deconfliction between friendly units. | Direct watch teams in the operation of command and control systems and displays. | Establish and enforce communications security and information assurance procedures. | Evaluate threat warnings and recommend defensive actions to senior commanders. | Prepare operation orders, situation reports, and briefings for command staff. | Supervise the maintenance and configuration of command center equipment and networks. | Train and certify watch personnel on console operations and emergency procedures. | Conduct exercises and drills to validate command and control procedures. | Maintain logs of operational events, communications traffic, and decisions taken. | Coordinate with allied and interagency partners during joint and combined operations.</t>
+  </si>
+  <si>
+    <t>55-1016.00</t>
+  </si>
+  <si>
+    <t>Infantry Officers</t>
+  </si>
+  <si>
+    <t>Infantry Officer | Infantry Platoon Leader | Rifle Company Commander | Infantry Company Commander | Platoon Commander | Weapons Platoon Commander | Ground Combat Officer | Infantry Unit Commander | Rifle Platoon Leader | Mechanized Infantry Officer</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Geography | Administration and Management | Telecommunications | English Language | Personnel and Human Resources | Education and Training | Transportation | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Reaction Time</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Dealing with Violent or Physically Aggressive People | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Spend Time Walking or Running | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Direct, train, and lead infantry units in ground combat operations. Duties include directing deployment of infantry weapons, vehicles, and equipment; directing location, construction, and camouflage of infantry positions and equipment; managing field communications operations; coordinating with armor, artillery, and air support units; performing strategic and tactical planning, including battle plan development; and leading basic reconnaissance operations.</t>
+  </si>
+  <si>
+    <t>Direct, train, and lead infantry units in ground combat operations. | Direct the deployment of infantry weapons, vehicles, and equipment. | Direct the location, construction, and camouflage of infantry positions and equipment. | Manage field communications operations and coordinate with armored and air support units. | Develop and issue operation orders, patrol plans, and rules of engagement. | Evaluate terrain and enemy dispositions to plan offensive and defensive operations. | Coordinate supporting fires from artillery, mortars, and close air support. | Supervise the accountability, maintenance, and serviceability of unit weapons and equipment. | Train subordinates in marksmanship, tactics, first aid, and survival techniques. | Enforce discipline, safety standards, and adherence to the law of armed conflict. | Monitor the health, welfare, and morale of assigned personnel. | Coordinate logistics, resupply, and casualty evacuation for the unit. | Conduct after-action reviews and prepare reports on unit performance. | Assess and report intelligence gathered during patrols and engagements. | Advise senior commanders on the tactical employment of infantry forces.</t>
+  </si>
+  <si>
+    <t>55-1017.00</t>
+  </si>
+  <si>
+    <t>Special Forces Officers</t>
+  </si>
+  <si>
+    <t>Special Forces Officer | Special Operations Officer | Detachment Commander | Special Forces Detachment Commander | SEAL Officer | Combat Diver Officer | Special Warfare Officer | Special Tactics Officer | Unconventional Warfare Officer | Special Operations Team Leader</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Geography | Foreign Language | Administration and Management | Telecommunications | Sociology and Anthropology | English Language | Education and Training | Psychology | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Reaction Time | Memorization</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Dealing with Violent or Physically Aggressive People | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Spend Time Walking or Running | Exposed to High Places</t>
+  </si>
+  <si>
+    <t>Lead elite teams that implement unconventional operations by air, land, or sea during combat or peacetime. These activities include offensive raids, demolitions, reconnaissance, search and rescue, and counterterrorism. In addition to their combat training, special forces officers often have specialized training in swimming, diving, parachuting, survival, emergency medicine, and foreign languages. Duties include directing advanced reconnaissance operations and evaluating intelligence information; recruiting, training, and equipping friendly forces; leading raids and invasions on enemy territories; training personnel to implement individual missions and contingency plans; performing strategic and tactical planning for politically sensitive missions; and operating sophisticated communications equipment.</t>
+  </si>
+  <si>
+    <t>Lead elite teams that implement unconventional operations by air, land, or sea during combat or peacetime. | Plan and direct offensive raids, demolitions, reconnaissance, search and rescue, and counterterrorism operations. | Conduct mission analysis and develop detailed operational plans and contingency options. | Direct infiltration and exfiltration operations using airborne, waterborne, and ground methods. | Coordinate operations with allied forces, host nation units, and interagency partners. | Train, advise, and assist foreign military and paramilitary personnel. | Direct the collection and reporting of intelligence in denied or hostile environments. | Supervise the maintenance, accountability, and readiness of specialized weapons and equipment. | Establish and enforce operational security and communications security procedures. | Evaluate team readiness and conduct advanced training in languages, medicine, demolitions, and communications. | Direct emergency medical treatment and casualty evacuation in remote environments. | Assess political, cultural, and terrain factors affecting mission execution. | Prepare mission briefs, debriefs, and after-action reports for higher headquarters. | Enforce adherence to rules of engagement and the law of armed conflict. | Advise senior commanders on special operations capabilities and employment.</t>
+  </si>
+  <si>
+    <t>55-1019.00</t>
+  </si>
+  <si>
+    <t>Military Officer Special and Tactical Operations Leaders, All Other</t>
+  </si>
+  <si>
+    <t>Special Operations Officer | Tactical Operations Officer | Combat Arms Officer | Military Operations Officer | Tactical Operations Leader | Combat Operations Officer | Military Tactical Officer | Operations Leader | Military Unit Commander | Tactical Unit Leader</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Administration and Management | Geography | Telecommunications | English Language | Personnel and Human Resources | Education and Training | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Spatial Orientation | Reaction Time | Stamina</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>All military officer special and tactical operations leaders not listed separately.</t>
+  </si>
+  <si>
+    <t>Plan, direct, and lead military special and tactical operations not classified separately. | Develop operation orders, tactical plans, and rules of engagement for assigned missions. | Direct the deployment and employment of unit personnel, weapons, and equipment. | Coordinate operations with supporting arms, adjacent units, and higher headquarters. | Supervise the training, readiness, and professional development of assigned personnel. | Enforce safety standards, discipline, and compliance with the law of armed conflict. | Monitor logistics, maintenance, and supply status to sustain unit operations. | Evaluate terrain, threat, and mission variables to inform tactical decisions. | Prepare readiness reports, after-action reviews, and briefings for command staff. | Supervise the accountability and security of weapons, ammunition, and classified materials. | Direct emergency and contingency procedures during operations and exercises. | Advise senior commanders on unit capabilities, limitations, and employment options.</t>
+  </si>
+  <si>
+    <t>55-2011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Air Crew Members</t>
+  </si>
+  <si>
+    <t>Air Crew Chief | Air Crew Supervisor | Aircrew Flight Equipment Supervisor | Flight Engineer Supervisor | Loadmaster Supervisor | Senior Air Crew Member | Air Crew Team Leader | Flight Crew Chief | Aircrew Section Supervisor | Airborne Systems Supervisor</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Mechanical | Telecommunications | Administration and Management | Education and Training | English Language | Computers and Electronics | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Auditory Attention | Reaction Time | Manual Dexterity | Control Precision</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Conditions | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of air crew members. Supervisors may also perform the same activities as the workers they supervise.</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of air crew members during flight and ground operations. | Assign duties and flight schedules to air crew personnel based on qualifications and mission requirements. | Perform the same in-flight duties as the crew members supervised, including operating communications and detection equipment. | Conduct preflight briefings and verify crew readiness, equipment status, and mission documentation. | Inspect aircraft mission equipment, survival gear, and safety systems before and after flight. | Train and certify crew members on aircraft systems, emergency procedures, and survival techniques. | Monitor crew performance during missions and provide corrective instruction. | Enforce flight safety regulations, crew rest requirements, and operating procedures. | Coordinate with maintenance personnel to resolve aircraft discrepancies. | Supervise the loading, securing, and offloading of cargo, equipment, and passengers. | Maintain flight records, training records, and equipment inventories. | Prepare postflight reports documenting mission results and equipment malfunctions. | Evaluate crew qualifications and recommend personnel for advancement or additional training. | Coordinate crew participation in exercises, evaluations, and readiness inspections.</t>
+  </si>
+  <si>
+    <t>55-2012.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Weapons Specialists/Crew Members</t>
+  </si>
+  <si>
+    <t>Armament Supervisor | Gunnery Sergeant | Ordnance Supervisor | Weapons Crew Chief | Weapons Section Chief | Weapons Specialist Supervisor | Armament Systems Supervisor | Fire Control Supervisor | Munitions Supervisor | Weapons Team Leader</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Radar software | Maintenance management software | Microsoft Excel | Microsoft Word | Email software | Simulation and modeling software | Navigation software | Digital mapping software | Logistics management information LMI database software | Microsoft PowerPoint | Satellite database software</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Mechanical | Engineering and Technology | Administration and Management | Education and Training | Physics | English Language | Computers and Electronics | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Manual Dexterity | Arm-Hand Steadiness | Control Precision | Reaction Time | Static Strength</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Avionics Technicians | Industrial Machinery Mechanics | Mobile Heavy Equipment Mechanics, Except Engines | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Telecommunications Equipment Installers and Repairers, Except Line Installers | Radio, Cellular, and Tower Equipment Installers and Repairers | Riggers | Crane and Tower Operators | Operating Engineers and Other Construction Equipment Operators | Ship Engineers | Sailors and Marine Oilers | Captains, Mates, and Pilots of Water Vessels | Airfield Operations Specialists | Logisticians | Transportation, Storage, and Distribution Managers | General and Operations Managers | Occupational Health and Safety Specialists | Training and Development Specialists | Explosives Workers, Ordnance Handling Experts, and Blasters</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of weapons specialists/crew members. Supervisors may also perform the same activities as the workers they supervise.</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of weapons specialists and crew members. | Perform the same duties as the weapons specialists supervised, including operating and maintaining weapons systems. | Assign crew positions and duties based on qualifications and mission requirements. | Direct the inspection, testing, and maintenance of weapons and fire control systems. | Enforce ammunition handling, storage, transport, and accountability procedures. | Train and certify crew members in gunnery, safety, and emergency procedures. | Supervise the loading, arming, and safing of weapons and munitions. | Verify compliance with technical orders, safety regulations, and rules of engagement. | Diagnose weapons system malfunctions and direct corrective maintenance actions. | Maintain maintenance records, ammunition inventories, and training documentation. | Conduct pre-fire and post-fire inspections of weapons and support equipment. | Evaluate crew performance during live-fire exercises and qualification events. | Coordinate resupply of ammunition, repair parts, and support equipment. | Prepare readiness reports and recommend improvements to weapons employment procedures.</t>
+  </si>
+  <si>
+    <t>55-2013.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of All Other Tactical Operations Specialists</t>
+  </si>
+  <si>
+    <t>Operations Sergeant | Platoon Sergeant | Section Chief | Squad Leader | Tactical Operations Supervisor | Team Leader | Senior Tactical Specialist | Tactical Section Supervisor | First Sergeant | Tactical Operations Chief</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Administration and Management | Education and Training | Geography | Telecommunications | English Language | Personnel and Human Resources | Transportation | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Spatial Orientation | Reaction Time | Stamina | Static Strength</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of all other tactical operations specialists not classified separately above. Supervisors may also perform the same activities as the workers they supervise.</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate the activities of tactical operations specialists not classified separately. | Perform the same duties as the specialists supervised during tactical operations. | Assign tasks, positions, and duty schedules based on qualifications and mission needs. | Train subordinates in tactics, weapons handling, communications, and first aid. | Enforce safety standards, discipline, and adherence to operating procedures. | Inspect personnel, weapons, and equipment for serviceability and combat readiness. | Coordinate unit movement, resupply, and communications during operations. | Monitor the health, welfare, and morale of assigned personnel. | Evaluate individual and team performance and conduct corrective training. | Maintain accountability records for personnel, weapons, and sensitive equipment. | Conduct pre-mission briefings and post-mission debriefings. | Prepare readiness, training, and after-action reports for the chain of command. | Advise unit officers on personnel capabilities and training requirements. | Direct emergency and contingency procedures during operations and exercises.</t>
+  </si>
+  <si>
+    <t>55-3011.00</t>
+  </si>
+  <si>
+    <t>Air Crew Members</t>
+  </si>
+  <si>
+    <t>Aerial Gunner | Airborne Cryptologic Operator | Air Crew Member | Flight Engineer | Loadmaster | Sensor Operator | Aerial Sensor Operator | Airborne Mission Systems Specialist | Boom Operator | Flight Crew Member</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Speaking | Reading Comprehension | Active Learning</t>
+  </si>
+  <si>
+    <t>Transportation | Mechanical | Telecommunications | Public Safety and Security | Computers and Electronics | English Language | Geography | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Conditions | Exposed to Whole Body Vibration | Spend Time Sitting | Exposed to Cramped Work Space, Awkward Positions | Coordinate or Lead Others in Accomplishing Work Activities | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection</t>
+  </si>
+  <si>
+    <t>Perform in-flight duties to ensure the successful completion of combat, reconnaissance, transport, and search and rescue missions. Duties include operating aircraft communications and detection equipment, including establishing satellite linkages and jamming enemy communications capabilities; conducting preflight, in-flight, and postflight inspections of onboard equipment; operating and maintaining aircraft weapons and defensive systems; operating and maintaining aircraft in-flight refueling systems; executing aircraft safety and emergency procedures; computing and verifying passenger, cargo, fuel, and emergency and special equipment weight and balance data; and conducting cargo and personnel drops.</t>
+  </si>
+  <si>
+    <t>Perform in-flight duties to ensure the successful completion of combat, reconnaissance, transport, and search and rescue missions. | Operate aircraft communications and detection equipment, including establishing satellite linkages and jamming enemy communications capabilities. | Conduct preflight inspections of aircraft mission equipment, survival gear, and safety systems. | Monitor radar, sonar, and electronic sensor displays to detect and track contacts. | Operate airborne weapons systems and defensive countermeasures during missions. | Compute weight and balance data and supervise the loading and securing of cargo and personnel. | Perform in-flight troubleshooting and minor repairs of aircraft systems. | Operate hoists, winches, and rescue equipment during search and rescue operations. | Administer emergency first aid to injured personnel during flight. | Record mission data, equipment readings, and system malfunctions in flight logs. | Communicate with ground stations, air traffic control, and other aircraft during missions. | Perform postflight inspections and report discrepancies to maintenance personnel. | Participate in survival, evasion, resistance, and escape training exercises. | Maintain proficiency in emergency egress, ditching, and bailout procedures.</t>
+  </si>
+  <si>
+    <t>55-3012.00</t>
+  </si>
+  <si>
+    <t>Aircraft Launch and Recovery Specialists</t>
+  </si>
+  <si>
+    <t>Aviation Boatswains Mate | Arresting Gear Operator | Catapult Operator | Flight Deck Crew Member | Launch and Recovery Specialist | Aircraft Handler | Aircraft Director | Landing Signal Enlisted Specialist | Flight Deck Technician | Aircraft Launch Specialist</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Engineering and Technology | Transportation | Physics | English Language | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing | Manual Dexterity | Arm-Hand Steadiness | Control Precision</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Spend Time Bending or Twisting Your Body | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Operate and maintain catapults, arresting gear, and associated mechanical, hydraulic, and control systems involved primarily in aircraft carrier takeoff and landing operations. Duties include installing and maintaining visual landing aids; testing and maintaining launch and recovery equipment using electric and mechanical test equipment and hand tools; activating airfield arresting systems, such as crash barriers and cables, during emergency landing situations; directing aircraft launch and recovery operations using hand or light signals; and maintaining logs of airplane launches, recoveries, and equipment maintenance.</t>
+  </si>
+  <si>
+    <t>Operate and maintain catapults, arresting gear, and associated mechanical, hydraulic, and control systems. | Install and maintain visual landing aids used during aircraft recovery operations. | Test and maintain launch and recovery equipment using electrical and mechanical test devices. | Direct aircraft movement, spotting, and tie-down operations on flight decks and hangar bays. | Set catapult and arresting gear configurations based on aircraft type, weight, and wind conditions. | Inspect cables, sheaves, hydraulic lines, and fittings for wear, damage, and correct tension. | Perform scheduled and unscheduled maintenance on launch and recovery machinery. | Operate firefighting, crash, and salvage equipment during flight deck emergencies. | Handle and service aircraft fuel, lubricants, and support equipment. | Enforce flight deck safety procedures and foreign object damage prevention measures. | Record equipment operating hours, maintenance actions, and launch and recovery cycles. | Assist in the rigging and removal of barricades and emergency recovery equipment. | Communicate with flight deck control using hand signals, radios, and sound-powered telephones. | Train junior personnel in equipment operation and flight deck safety.</t>
+  </si>
+  <si>
+    <t>55-3013.00</t>
+  </si>
+  <si>
+    <t>Armored Assault Vehicle Crew Members</t>
+  </si>
+  <si>
+    <t>Amphibious Assault Vehicle Crewman | Armor Crewman | Cavalry Scout | Tank Crew Member | Tank Driver | Tank Gunner | Tank Loader | Armored Vehicle Driver | Armor Crew Member | Assault Vehicle Crewman</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Transportation | Geography | Telecommunications | English Language | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing | Manual Dexterity | Arm-Hand Steadiness | Control Precision | Rate Control</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Cramped Work Space, Awkward Positions | Exposed to Whole Body Vibration | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Operate tanks, light armor, and amphibious assault vehicles during combat situations on land or in aquatic environments. Duties include driving armored vehicles that require specialized training; operating and maintaining targeting and firing systems; operating and maintaining advanced onboard communications and navigation equipment; transporting personnel and equipment in a combat environment; and operating and maintaining auxiliary weapons, including machine guns and grenade launchers.</t>
+  </si>
+  <si>
+    <t>Operate tanks, light armor, and amphibious assault vehicles during combat operations on land or in aquatic environments. | Drive armored vehicles that require specialized training over roads, cross-country, and through obstacles. | Operate and maintain targeting and firing systems, including main guns and machine guns. | Operate and maintain advanced onboard communications and navigation equipment. | Load, stow, and account for main gun ammunition and small arms munitions. | Perform operator-level maintenance, inspections, and fault diagnosis on vehicle systems. | Observe and report enemy positions, terrain conditions, and obstacles to the vehicle commander. | Camouflage and conceal vehicles and prepare fighting positions. | Conduct reconnaissance and security patrols in support of maneuver operations. | Recover disabled vehicles using towing and self-recovery equipment. | Apply nuclear, biological, and chemical defense measures and decontamination procedures. | Maintain vehicle logbooks, maintenance records, and ammunition accountability documents. | Perform preventive maintenance checks and services before, during, and after operations. | Participate in gunnery qualification and crew drill exercises.</t>
+  </si>
+  <si>
+    <t>55-3014.00</t>
+  </si>
+  <si>
+    <t>Artillery and Missile Crew Members</t>
+  </si>
+  <si>
+    <t>Air Defense Artillery Crewmember | Artillery Crew Member | Cannon Crewmember | Field Artillery Crewman | Fire Control Specialist | Gunners Mate | Missile Crew Member | Howitzer Crewmember | Naval Gunners Mate | Artillery Gunner</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Speaking | Reading Comprehension | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>Mathematics | Mechanical | Public Safety and Security | Physics | Geography | Engineering and Technology | English Language | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing | Mathematical Reasoning | Number Facility | Manual Dexterity | Arm-Hand Steadiness</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Outdoors, Under Cover</t>
+  </si>
+  <si>
+    <t>Target, fire, and maintain weapons used to destroy enemy positions, aircraft, and vessels. Field artillery crew members predominantly use guns, cannons, and howitzers in ground combat operations, while air defense artillery crew members predominantly use missiles and rockets. Naval artillery crew members predominantly use torpedoes and missiles launched from a ship or submarine. Duties include testing, inspecting, and storing ammunition, missiles, and torpedoes; conducting preventive and routine maintenance on weapons and related equipment; establishing and maintaining radio and wire communications; and operating weapons targeting, firing, and launch computer systems.</t>
+  </si>
+  <si>
+    <t>Target, fire, and maintain weapons used to destroy enemy positions, aircraft, and vessels. | Operate guns, cannons, and howitzers in ground combat operations. | Operate missile and rocket systems in air defense and naval gunfire operations. | Compute and apply firing data, including deflection, elevation, charge, and fuze settings. | Load, stow, and account for artillery ammunition, propellants, and fuzes. | Emplace, level, and lay weapons systems using aiming circles, collimators, and sights. | Perform operator maintenance and functional checks on guns, launchers, and fire control equipment. | Establish and operate field communications between gun sections and fire direction centers. | Prepare and occupy firing positions, including camouflage and ammunition pits. | Observe and report the effects of fire and adjust subsequent rounds. | Apply safety procedures for handling, transporting, and storing munitions. | Perform crew drills to achieve required rates of fire and response times. | Maintain ammunition expenditure records and equipment maintenance logs. | Apply nuclear, biological, and chemical defense and decontamination procedures.</t>
+  </si>
+  <si>
+    <t>55-3015.00</t>
+  </si>
+  <si>
+    <t>Command and Control Center Specialists</t>
+  </si>
+  <si>
+    <t>Air Traffic Control Operator | Combat Control Specialist | Command and Control Specialist | Operations Specialist | Radar Operator | Tactical Data Systems Operator | Air Defense Systems Operator | Combat Information Center Operator | Command Post Specialist | Battle Management Specialist</t>
+  </si>
+  <si>
+    <t>Telecommunications | Computers and Electronics | Public Safety and Security | Geography | English Language | Transportation | Communications and Media | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing | Perceptual Speed | Flexibility of Closure | Speed of Closure | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Spend Time Sitting | Importance of Repeating Same Tasks | Degree of Automation | E-Mail | Telephone Conversations | Written Letters and Memos | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Operate and monitor communications, detection, and weapons systems essential for controlling air, ground, and naval operations. Duties include maintaining and relaying critical communications between air, naval, and ground forces; implementing emergency plans for natural and wartime disasters; relaying command center information to high-level military and government decisionmakers; monitoring surveillance and detection systems, such as air defense; interpreting and evaluating tactical situations and making recommendations to superiors; and operating weapons targeting, firing, and launch computer systems.</t>
+  </si>
+  <si>
+    <t>Operate and monitor communications, detection, and weapons systems essential for controlling air, ground, and naval operations. | Maintain and relay critical communications between air, naval, and ground forces. | Implement emergency plans for natural and wartime disasters. | Relay command directives to operational units and confirm receipt and execution. | Monitor radar and sensor displays to detect, identify, and track air and surface contacts. | Plot and record contact positions, tracks, and engagement data on tactical displays. | Operate secure voice and data communications equipment and cryptographic devices. | Perform operator maintenance and functional checks on command and control equipment. | Compile situation reports, watch logs, and message traffic for command staff. | Coordinate airspace control measures and identification procedures with adjacent units. | Apply communications security and information assurance procedures. | Participate in exercises and drills to validate operating procedures. | Alert command personnel to threat warnings and system malfunctions. | Train junior personnel on console operations and emergency procedures.</t>
+  </si>
+  <si>
+    <t>55-3016.00</t>
+  </si>
+  <si>
+    <t>Infantry</t>
+  </si>
+  <si>
+    <t>Combat Engineer | Grenadier | Indirect Fire Infantryman | Infantryman | Machine Gunner | Mortarman | Rifleman | Infantry Soldier | Antiarmor Infantryman | Scout</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Geography | Mechanical | Telecommunications | English Language | Transportation | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing | Trunk Strength | Dynamic Strength | Extent Flexibility | Night Vision</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Dealing with Violent or Physically Aggressive People | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Spend Time Walking or Running | Spend Time Standing | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Operate weapons and equipment in ground combat operations. Duties include operating and maintaining weapons, such as rifles, machine guns, mortars, and hand grenades; locating, constructing, and camouflaging infantry positions and equipment; evaluating terrain and recording topographical information; operating and maintaining field communications equipment; assessing need for and directing supporting fire; placing explosives and performing minesweeping activities on land; and participating in basic reconnaissance operations.</t>
+  </si>
+  <si>
+    <t>Operate weapons and equipment in ground combat operations. | Operate and maintain weapons such as rifles, machine guns, mortars, and hand grenades. | Locate, construct, and camouflage infantry positions and equipment. | Evaluate terrain and record topographical information for use in tactical planning. | Conduct offensive, defensive, and reconnaissance patrols in varied terrain and weather. | Perform preventive maintenance and functions checks on individual and crew-served weapons. | Employ hand and arm signals, field radios, and wire communications during operations. | Detect, mark, and avoid mines, booby traps, and improvised explosive devices. | Administer first aid and perform casualty evacuation under combat conditions. | Load, unload, and account for ammunition, rations, and unit equipment. | Apply nuclear, biological, and chemical defense and decontamination procedures. | Conduct search operations and process detainees according to established rules. | Participate in marksmanship qualification, physical conditioning, and field training exercises. | Report enemy activity, terrain conditions, and mission results to the chain of command.</t>
+  </si>
+  <si>
+    <t>55-3018.00</t>
+  </si>
+  <si>
+    <t>Special Forces</t>
+  </si>
+  <si>
+    <t>Combat Controller | Explosive Ordnance Disposal Specialist | Pararescue Specialist | Special Forces Communications Sergeant | Special Forces Medical Sergeant | Special Forces Weapons Sergeant | Special Operations Specialist | Combat Diver | SEAL Operator | Special Warfare Operator</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Speaking | Reading Comprehension | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Geography | Foreign Language | Telecommunications | Medicine and Dentistry | English Language | Sociology and Anthropology | Education and Training | Mechanical</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Far Vision | Near Vision | Selective Attention | Reaction Time | Information Ordering | Inductive Reasoning | Auditory Attention | Multilimb Coordination | Spatial Orientation | Stamina | Static Strength | Gross Body Coordination | Depth Perception | Time Sharing | Trunk Strength | Dynamic Strength | Memorization | Night Vision | Gross Body Equilibrium</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Dealing with Violent or Physically Aggressive People | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Spend Time Walking or Running | Exposed to High Places | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Keeping or Regaining Balance</t>
+  </si>
+  <si>
+    <t>Implement unconventional operations by air, land, or sea during combat or peacetime as members of elite teams. These activities include offensive raids, demolitions, reconnaissance, search and rescue, and counterterrorism. In addition to their combat training, special forces members often have specialized training in swimming, diving, parachuting, survival, emergency medicine, and foreign languages. Duties include conducting advanced reconnaissance operations and collecting intelligence information; recruiting, training, and equipping friendly forces; conducting raids and invasions on enemy territories; laying and detonating explosives for demolition targets; locating, identifying, defusing, and disposing of ordnance; and operating and maintaining sophisticated communications equipment.</t>
+  </si>
+  <si>
+    <t>Implement unconventional operations by air, land, or sea during combat or peacetime as members of elite teams. | Execute offensive raids, demolitions, reconnaissance, search and rescue, and counterterrorism missions. | Conduct infiltration and exfiltration by parachute, small boat, submersible, and overland movement. | Operate and maintain specialized weapons, demolitions, and communications equipment. | Collect, record, and report intelligence gathered in denied or hostile environments. | Train and advise foreign military and paramilitary personnel in tactics and weapons employment. | Provide emergency medical treatment and trauma care in remote environments. | Establish and operate long-range and satellite communications networks. | Prepare and employ explosive charges for demolition and breaching operations. | Conduct close quarters battle, sniping, and small unit tactics. | Perform underwater operations including combat diving and ship attack. | Navigate over land, sea, and air using map, compass, and electronic navigation aids. | Apply survival, evasion, resistance, and escape techniques. | Prepare mission plans, target folders, and post-mission debriefing reports.</t>
+  </si>
+  <si>
+    <t>55-3019.00</t>
+  </si>
+  <si>
+    <t>Military Enlisted Tactical Operations and Air/Weapons Specialists and Crew Members, All Other</t>
+  </si>
+  <si>
+    <t>Air and Weapons Specialist | Combat Operations Specialist | Military Crew Member | Tactical Operations Specialist | Weapons Specialist | Enlisted Tactical Specialist | Combat Support Specialist | Military Specialist | Tactical Systems Operator | Operations Crew Member</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Mechanical | Telecommunications | Geography | English Language | Computers and Electronics | Transportation</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>All military enlisted tactical operations and air/weapons specialists and crewmembers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform tactical operations and air or weapons specialist duties not classified separately. | Operate and maintain assigned weapons, vehicles, and mission equipment. | Execute assigned tasks during combat, training, and support operations. | Monitor and operate communications and detection equipment. | Perform operator-level maintenance, inspections, and functional checks. | Handle, transport, and account for ammunition and sensitive equipment. | Apply safety procedures and protective measures during operations. | Record operational data, equipment readings, and maintenance actions. | Participate in drills, exercises, and readiness evaluations. | Apply nuclear, biological, and chemical defense and decontamination procedures. | Administer first aid and assist with casualty evacuation. | Report mission results, equipment status, and observations to supervisors.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +776,606 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>111</v>
+      </c>
+      <c r="K13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" t="s">
+        <v>134</v>
+      </c>
+      <c r="H16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>143</v>
+      </c>
+      <c r="K17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>